--- a/Apr_15_ConditionalFunctional.20260415113706091.xlsx
+++ b/Apr_15_ConditionalFunctional.20260415113706091.xlsx
@@ -1,25 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f009553a5688ab78/Documents/Desktop/Bytecode_training/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_CD756894645FB936B455ACD68D37F3B4289735EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8F3B225-BB7D-4D05-B508-CAD9152E4C25}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="If &amp; Ifs Notes" sheetId="4" r:id="rId1"/>
     <sheet name="Conditional Functions DAtaset" sheetId="3" r:id="rId2"/>
-    <sheet name="Table Calculation" sheetId="1" r:id="rId3"/>
-    <sheet name="Cell Reference Data" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="Table Calculation" sheetId="1" r:id="rId4"/>
+    <sheet name="Cell Reference Data" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conditional Functions DAtaset'!$H$13:$I$17</definedName>
     <definedName name="Category">'Conditional Functions DAtaset'!$E$2:$E$1048576</definedName>
     <definedName name="Cust_Name">'Conditional Functions DAtaset'!$C$2:$C$1048576</definedName>
     <definedName name="Region">'Conditional Functions DAtaset'!$D$2:$D$1048576</definedName>
+    <definedName name="Sale_datas">'Conditional Functions DAtaset'!$C:$F</definedName>
     <definedName name="Sales">'Conditional Functions DAtaset'!$F$2:$F$1048576</definedName>
     <definedName name="sum">'Cell Reference Data'!$F:$F</definedName>
-    <definedName name="Sale_datas">'Conditional Functions DAtaset'!$C:$F</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,8 +37,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>"Conditional Aggregate Functions in Excel (IF &amp; IFS Functions)"</t>
   </si>
@@ -384,14 +389,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,151 +423,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,192 +439,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1081,262 +781,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1344,36 +796,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1409,69 +843,53 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1729,243 +1147,240 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C1:P29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C2:P29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="88.9074074074074" customWidth="1"/>
-    <col min="4" max="4" width="48.5462962962963" customWidth="1"/>
-    <col min="5" max="5" width="38.5462962962963" customWidth="1"/>
+    <col min="3" max="3" width="88.88671875" customWidth="1"/>
+    <col min="4" max="4" width="48.5546875" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15"/>
-    <row r="2" ht="24.15" spans="3:16">
-      <c r="C2" s="32" t="s">
+    <row r="2" spans="3:16" ht="23.4">
+      <c r="C2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="34"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="25"/>
     </row>
     <row r="4" spans="3:16">
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="38" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="3:16">
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="26" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="3:16">
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="27" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="3:16">
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="3:16">
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="26" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="3:16">
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="3:16">
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="26" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" ht="15.6" spans="3:16">
-      <c r="C13" s="37" t="s">
+    <row r="13" spans="3:16" ht="15.6">
+      <c r="C13" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" ht="26.25" customHeight="1" spans="3:16">
-      <c r="C14" s="38" t="s">
+    <row r="14" spans="3:16" ht="26.25" customHeight="1">
+      <c r="C14" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40" t="s">
+      <c r="F14" s="31"/>
+      <c r="G14" s="31" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="43.2" spans="3:16">
-      <c r="C15" s="41" t="s">
+    <row r="15" spans="3:16" ht="43.2">
+      <c r="C15" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="43" t="s">
+      <c r="F15" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="G15" s="33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="3:16">
-      <c r="C16" s="44" t="s">
+    <row r="16" spans="3:16" ht="28.8">
+      <c r="C16" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="45" t="s">
+      <c r="F16" s="2"/>
+      <c r="G16" s="36" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="3:4">
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="37" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="3:4">
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="3:4">
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="37" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="2" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:P37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="8" max="8" width="47.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="29.8148148148148" customWidth="1"/>
-    <col min="11" max="16" width="13.6296296296296" customWidth="1"/>
+    <col min="8" max="8" width="47.6640625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
+    <col min="11" max="16" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16">
@@ -1984,720 +1399,720 @@
       <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="J1" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="2:16">
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>7899</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="27" t="s">
+      <c r="H2" s="42"/>
+      <c r="I2" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="5" cm="1">
+      <c r="L2" s="2" cm="1">
         <f t="array" ref="L2">SUMIF(Cust_Name,K2,Sales)</f>
         <v>27881</v>
       </c>
-      <c r="M2" s="28" cm="1">
+      <c r="M2" s="20" cm="1">
         <f t="array" ref="M2">AVERAGEIF(Cust_Name,K2,Sales)</f>
-        <v>4646.83333333333</v>
-      </c>
-      <c r="N2" s="5" cm="1">
+        <v>4646.8333333333303</v>
+      </c>
+      <c r="N2" s="2" cm="1">
         <f t="array" ref="N2">COUNTIF(Cust_Name,K2)</f>
         <v>6</v>
       </c>
-      <c r="O2" s="5" cm="1">
+      <c r="O2" s="2" cm="1">
         <f t="array" ref="O2">_xlfn.MINIFS(Sales,Cust_Name,K2)</f>
         <v>1682</v>
       </c>
-      <c r="P2" s="5" cm="1">
+      <c r="P2" s="2" cm="1">
         <f t="array" ref="P2">_xlfn.MAXIFS(Sales,Cust_Name,K2)</f>
         <v>7830</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5">
+      <c r="B3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <v>6146</v>
       </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="27" t="s">
+      <c r="H3" s="42"/>
+      <c r="I3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="5" cm="1">
+      <c r="L3" s="2" cm="1">
         <f t="array" ref="L3">SUMIF(Cust_Name,K3,Sales)</f>
         <v>23362</v>
       </c>
-      <c r="M3" s="28" cm="1">
+      <c r="M3" s="20" cm="1">
         <f t="array" ref="M3">AVERAGEIF(Cust_Name,K3,Sales)</f>
-        <v>3893.66666666667</v>
-      </c>
-      <c r="N3" s="5" cm="1">
+        <v>3893.6666666666702</v>
+      </c>
+      <c r="N3" s="2" cm="1">
         <f t="array" ref="N3">COUNTIF(Cust_Name,K3)</f>
         <v>6</v>
       </c>
-      <c r="O3" s="5" cm="1">
+      <c r="O3" s="2" cm="1">
         <f t="array" ref="O3">_xlfn.MINIFS(Sales,Cust_Name,K3)</f>
         <v>2087</v>
       </c>
-      <c r="P3" s="5" cm="1">
+      <c r="P3" s="2" cm="1">
         <f t="array" ref="P3">_xlfn.MAXIFS(Sales,Cust_Name,K3)</f>
         <v>8044</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5">
+      <c r="B4" s="2">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>8196</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="27" t="s">
+      <c r="H4" s="42"/>
+      <c r="I4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="5" cm="1">
+      <c r="L4" s="2" cm="1">
         <f t="array" ref="L4">SUMIF(Cust_Name,K4,Sales)</f>
         <v>38906</v>
       </c>
-      <c r="M4" s="28" cm="1">
+      <c r="M4" s="20" cm="1">
         <f t="array" ref="M4">AVERAGEIF(Cust_Name,K4,Sales)</f>
-        <v>6484.33333333333</v>
-      </c>
-      <c r="N4" s="5" cm="1">
+        <v>6484.3333333333303</v>
+      </c>
+      <c r="N4" s="2" cm="1">
         <f t="array" ref="N4">COUNTIF(Cust_Name,K4)</f>
         <v>6</v>
       </c>
-      <c r="O4" s="5" cm="1">
+      <c r="O4" s="2" cm="1">
         <f t="array" ref="O4">_xlfn.MINIFS(Sales,Cust_Name,K4)</f>
         <v>4589</v>
       </c>
-      <c r="P4" s="5" cm="1">
+      <c r="P4" s="2" cm="1">
         <f t="array" ref="P4">_xlfn.MAXIFS(Sales,Cust_Name,K4)</f>
         <v>9166</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="2:16">
-      <c r="B5" s="5">
+    <row r="5" spans="2:16">
+      <c r="B5" s="2">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <v>5821</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30" t="s">
+      <c r="H5" s="43"/>
+      <c r="I5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="5" cm="1">
+      <c r="K5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="2" cm="1">
         <f t="array" ref="L5">SUMIF(Cust_Name,K5,Sales)</f>
         <v>101749</v>
       </c>
-      <c r="M5" s="28" cm="1">
+      <c r="M5" s="20" cm="1">
         <f t="array" ref="M5">AVERAGEIF(Cust_Name,K5,Sales)</f>
-        <v>5652.72222222222</v>
-      </c>
-      <c r="N5" s="5" cm="1">
+        <v>5652.7222222222199</v>
+      </c>
+      <c r="N5" s="2" cm="1">
         <f t="array" ref="N5">COUNTIF(Cust_Name,K5)</f>
         <v>18</v>
       </c>
-      <c r="O5" s="5" cm="1">
+      <c r="O5" s="2" cm="1">
         <f t="array" ref="O5">_xlfn.MINIFS(Sales,Cust_Name,K5)</f>
         <v>1309</v>
       </c>
-      <c r="P5" s="5" cm="1">
+      <c r="P5" s="2" cm="1">
         <f t="array" ref="P5">_xlfn.MAXIFS(Sales,Cust_Name,K5)</f>
         <v>9058</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5">
+      <c r="B6" s="2">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="2">
         <v>2087</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5">
+      <c r="B7" s="2">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="2">
         <v>7243</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="2">
         <f>SUMIF(C:C,"Ravi",F:F)</f>
         <v>101749</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5">
+      <c r="B8" s="2">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="2">
         <v>2394</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="2">
         <f>COUNTIF(C:C,"Ravi")</f>
         <v>18</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="5" cm="1">
+      <c r="L8" s="2" cm="1">
         <f t="array" ref="L8">SUMIF(Region,K8,Sales)</f>
         <v>43947</v>
       </c>
-      <c r="M8" s="28" cm="1">
+      <c r="M8" s="20" cm="1">
         <f t="array" ref="M8">AVERAGEIF(Region,K8,Sales)</f>
         <v>4883</v>
       </c>
-      <c r="N8" s="5" cm="1">
+      <c r="N8" s="2" cm="1">
         <f t="array" ref="N8">COUNTIF(Region,K8)</f>
         <v>9</v>
       </c>
-      <c r="O8" s="5" cm="1">
+      <c r="O8" s="2" cm="1">
         <f t="array" ref="O8">_xlfn.MINIFS(Sales,Region,K8)</f>
         <v>1309</v>
       </c>
-      <c r="P8" s="5"/>
+      <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5">
+      <c r="B9" s="2">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="2">
         <v>4907</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="2">
         <f>AVERAGEIF(D:D,"South",F:F)</f>
         <v>6037.4</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="5" cm="1">
+      <c r="L9" s="2" cm="1">
         <f t="array" ref="L9">SUMIF(Region,K9,Sales)</f>
         <v>56198</v>
       </c>
-      <c r="M9" s="28" cm="1">
+      <c r="M9" s="20" cm="1">
         <f t="array" ref="M9">AVERAGEIF(Region,K9,Sales)</f>
-        <v>5108.90909090909</v>
-      </c>
-      <c r="N9" s="5" cm="1">
+        <v>5108.9090909090901</v>
+      </c>
+      <c r="N9" s="2" cm="1">
         <f t="array" ref="N9">COUNTIF(Region,K9)</f>
         <v>11</v>
       </c>
-      <c r="O9" s="5" cm="1">
+      <c r="O9" s="2" cm="1">
         <f t="array" ref="O9">_xlfn.MINIFS(Sales,Region,K9)</f>
         <v>2087</v>
       </c>
-      <c r="P9" s="5"/>
+      <c r="P9" s="2"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5">
+      <c r="B10" s="2">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="2">
         <v>1309</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="2">
         <f>_xlfn.MAXIFS(F:F,E:E,"Electronics")</f>
         <v>9058</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L10" s="5" cm="1">
+      <c r="L10" s="2" cm="1">
         <f t="array" ref="L10">SUMIF(Region,K10,Sales)</f>
         <v>61566</v>
       </c>
-      <c r="M10" s="28" cm="1">
+      <c r="M10" s="20" cm="1">
         <f t="array" ref="M10">AVERAGEIF(Region,K10,Sales)</f>
-        <v>5596.90909090909</v>
-      </c>
-      <c r="N10" s="5" cm="1">
+        <v>5596.9090909090901</v>
+      </c>
+      <c r="N10" s="2" cm="1">
         <f t="array" ref="N10">COUNTIF(Region,K10)</f>
         <v>11</v>
       </c>
-      <c r="O10" s="5" cm="1">
+      <c r="O10" s="2" cm="1">
         <f t="array" ref="O10">_xlfn.MINIFS(Sales,Region,K10)</f>
         <v>1682</v>
       </c>
-      <c r="P10" s="5"/>
+      <c r="P10" s="2"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5">
+      <c r="B11" s="2">
         <v>10</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="2">
         <v>9166</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="2">
         <f>_xlfn.MINIFS(F:F,E:E,"Fashion")</f>
         <v>1338</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="5" cm="1">
+      <c r="L11" s="2" cm="1">
         <f t="array" ref="L11">SUMIF(Region,K11,Sales)</f>
         <v>30187</v>
       </c>
-      <c r="M11" s="28" cm="1">
+      <c r="M11" s="20" cm="1">
         <f t="array" ref="M11">AVERAGEIF(Region,K11,Sales)</f>
         <v>6037.4</v>
       </c>
-      <c r="N11" s="5" cm="1">
+      <c r="N11" s="2" cm="1">
         <f t="array" ref="N11">COUNTIF(Region,K11)</f>
         <v>5</v>
       </c>
-      <c r="O11" s="5" cm="1">
+      <c r="O11" s="2" cm="1">
         <f t="array" ref="O11">_xlfn.MINIFS(Sales,Region,K11)</f>
         <v>2695</v>
       </c>
-      <c r="P11" s="5"/>
+      <c r="P11" s="2"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="5">
+      <c r="B12" s="2">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="2">
         <v>4023</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="5">
+      <c r="B13" s="2">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="2">
         <v>1338</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="31"/>
-      <c r="K13" s="25" t="s">
+      <c r="I13" s="22"/>
+      <c r="K13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="L13" s="25" t="s">
+      <c r="L13" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M13" s="25" t="s">
+      <c r="M13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="25" t="s">
+      <c r="N13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O13" s="25" t="s">
+      <c r="O13" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="P13" s="25" t="s">
+      <c r="P13" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="5">
+      <c r="B14" s="2">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="2">
         <v>2695</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="22">
         <f>SUMIFS(F:F,D:D,"South")</f>
         <v>30187</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="5">
+      <c r="B15" s="2">
         <v>14</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="2">
         <v>7830</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="22">
         <f>COUNTIFS(E:E,"Electronics",D:D,"South")</f>
         <v>4</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="5">
+      <c r="B16" s="2">
         <v>15</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="2">
         <v>4154</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="22">
         <f>AVERAGEIFS(F:F,E:E,"Fashion",D:D,"North")</f>
         <v>5353.875</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="5">
+      <c r="B17" s="2">
         <v>16</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="2">
         <v>6381</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="22">
         <f>COUNTIFS(F:F,"&gt;5000")</f>
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="5">
+      <c r="B18" s="2">
         <v>17</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="2">
         <v>3387</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="5">
+      <c r="B19" s="2">
         <v>18</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="2">
         <v>7395</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="5">
+      <c r="B20" s="2">
         <v>19</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="2">
         <v>4368</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="5">
+      <c r="B21" s="2">
         <v>20</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="2">
         <v>4232</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="5">
+      <c r="B22" s="2">
         <v>21</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="2">
         <v>9058</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="5">
+      <c r="B23" s="2">
         <v>22</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="2">
         <v>4905</v>
       </c>
       <c r="H23" t="s">
@@ -2705,240 +2120,240 @@
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="5">
+      <c r="B24" s="2">
         <v>23</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="2">
         <v>3712</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="5">
+      <c r="B25" s="2">
         <v>24</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="2">
         <v>7555</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="5">
+      <c r="B26" s="2">
         <v>25</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="2">
         <v>5309</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="5">
+      <c r="B27" s="2">
         <v>26</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="2">
         <v>1682</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="5">
+      <c r="B28" s="2">
         <v>27</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="2">
         <v>3885</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="5">
+      <c r="B29" s="2">
         <v>28</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="2">
         <v>4589</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="5">
+      <c r="B30" s="2">
         <v>29</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="2">
         <v>2109</v>
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="5">
+      <c r="B31" s="2">
         <v>30</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="5" t="s">
+      <c r="C31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="2">
         <v>4006</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="5">
+      <c r="B32" s="2">
         <v>31</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="2">
         <v>8164</v>
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="5">
+      <c r="B33" s="2">
         <v>32</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="2">
         <v>3084</v>
       </c>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="5">
+      <c r="B34" s="2">
         <v>33</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="C34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="2">
         <v>8737</v>
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="5">
+      <c r="B35" s="2">
         <v>34</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="2">
         <v>8044</v>
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="5">
+      <c r="B36" s="2">
         <v>35</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="2">
         <v>8044</v>
       </c>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="5">
+      <c r="B37" s="2">
         <v>36</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="2">
         <v>8044</v>
       </c>
     </row>
@@ -2947,18 +2362,214 @@
     <mergeCell ref="H1:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75783AB-BA76-468B-9550-A67D45F2A8EC}">
+  <dimension ref="D2:D38"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:4">
+      <c r="D2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="4:4">
+      <c r="D3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="E2:O28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="15" max="15" width="9.66666666666667"/>
+    <col min="15" max="15" width="9.6640625"/>
   </cols>
   <sheetData>
     <row r="2" spans="5:15">
@@ -3134,34 +2745,34 @@
       </c>
     </row>
     <row r="18" spans="5:15">
-      <c r="F18" s="22">
+      <c r="F18" s="16">
         <v>1</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="16">
         <v>2</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="16">
         <v>3</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="16">
         <v>4</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="16">
         <v>5</v>
       </c>
-      <c r="K18" s="22">
+      <c r="K18" s="16">
         <v>6</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="16">
         <v>7</v>
       </c>
-      <c r="M18" s="22">
+      <c r="M18" s="16">
         <v>8</v>
       </c>
-      <c r="N18" s="22">
+      <c r="N18" s="16">
         <v>9</v>
       </c>
-      <c r="O18" s="22">
+      <c r="O18" s="16">
         <v>10</v>
       </c>
     </row>
@@ -3215,43 +2826,43 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:F29" si="3">$E20*F$18</f>
+        <f t="shared" ref="F20:F28" si="3">$E20*F$18</f>
         <v>2</v>
       </c>
       <c r="G20">
-        <f t="shared" ref="G20:G29" si="4">$E20*G$18</f>
+        <f t="shared" ref="G20:G28" si="4">$E20*G$18</f>
         <v>4</v>
       </c>
       <c r="H20">
-        <f t="shared" ref="H20:H29" si="5">$E20*H$18</f>
+        <f t="shared" ref="H20:H28" si="5">$E20*H$18</f>
         <v>6</v>
       </c>
       <c r="I20">
-        <f t="shared" ref="I20:I29" si="6">$E20*I$18</f>
+        <f t="shared" ref="I20:I28" si="6">$E20*I$18</f>
         <v>8</v>
       </c>
       <c r="J20">
-        <f t="shared" ref="J20:J29" si="7">$E20*J$18</f>
+        <f t="shared" ref="J20:J28" si="7">$E20*J$18</f>
         <v>10</v>
       </c>
       <c r="K20">
-        <f t="shared" ref="K20:K29" si="8">$E20*K$18</f>
+        <f t="shared" ref="K20:K28" si="8">$E20*K$18</f>
         <v>12</v>
       </c>
       <c r="L20">
-        <f t="shared" ref="L20:L29" si="9">$E20*L$18</f>
+        <f t="shared" ref="L20:L28" si="9">$E20*L$18</f>
         <v>14</v>
       </c>
       <c r="M20">
-        <f t="shared" ref="M20:M29" si="10">$E20*M$18</f>
+        <f t="shared" ref="M20:M28" si="10">$E20*M$18</f>
         <v>16</v>
       </c>
       <c r="N20">
-        <f t="shared" ref="N20:N29" si="11">$E20*N$18</f>
+        <f t="shared" ref="N20:N28" si="11">$E20*N$18</f>
         <v>18</v>
       </c>
       <c r="O20">
-        <f t="shared" ref="O20:O29" si="12">$E20*O$18</f>
+        <f t="shared" ref="O20:O28" si="12">$E20*O$18</f>
         <v>20</v>
       </c>
     </row>
@@ -3617,26 +3228,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B2:L48"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B3:L48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18.1759259259259" customWidth="1"/>
-    <col min="9" max="9" width="17.1759259259259" customWidth="1"/>
-    <col min="10" max="10" width="19.3611111111111" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="19.1759259259259" customWidth="1"/>
+    <col min="12" max="12" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="15.15"/>
-    <row r="3" ht="15.15" spans="2:12">
+    <row r="3" spans="2:12">
       <c r="B3" s="1" t="s">
         <v>44</v>
       </c>
@@ -3652,240 +3260,240 @@
       <c r="F3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="4"/>
-    </row>
-    <row r="4" ht="15.15" spans="2:12">
-      <c r="B4" s="5">
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="46"/>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>7899</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="2:12">
-      <c r="B5" s="5">
+    <row r="5" spans="2:12">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <v>6146</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="6">
         <f>SUM(sum)</f>
         <v>191898</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="7">
         <f>AVERAGE(sum)</f>
         <v>5330.5</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="7">
         <f>MIN(sum)</f>
         <v>1309</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="7">
         <f>MAX(sum)</f>
         <v>9166</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="8">
         <f>COUNT(sum)</f>
         <v>36</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="2:12">
-      <c r="B6" s="5">
+    <row r="6" spans="2:12">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="2">
         <v>8196</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="2:12">
-      <c r="B7" s="5">
+    <row r="7" spans="2:12">
+      <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="2">
         <v>5821</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" ht="15.15" spans="2:12">
-      <c r="B8" s="5">
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="49"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="2">
         <v>2087</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" ht="15.15" spans="2:12">
-      <c r="B9" s="5">
+    <row r="9" spans="2:12">
+      <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="2">
         <v>7243</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="12">
         <v>200000</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="13">
         <f>$H$5</f>
         <v>191898</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="14">
         <f>$H$5/$H$9</f>
-        <v>0.95949</v>
-      </c>
-      <c r="K9" s="19">
+        <v>0.95948999999999995</v>
+      </c>
+      <c r="K9" s="13">
         <f>$H$9-$H$5</f>
         <v>8102</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="15">
         <f>($H$9-$H$5)/$H$9</f>
-        <v>0.04051</v>
+        <v>4.0509999999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="5">
+      <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="2">
         <v>2394</v>
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="5">
+      <c r="B11" s="2">
         <v>8</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="2">
         <v>4907</v>
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="5">
+      <c r="B12" s="2">
         <v>9</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="2">
         <v>1309</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -3893,587 +3501,587 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="5">
+      <c r="B13" s="2">
         <v>10</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="2">
         <v>9166</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="2">
         <v>7899</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="5">
+      <c r="B14" s="2">
         <v>11</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="2">
         <v>4023</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="2">
         <v>6146</v>
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="5">
+      <c r="B15" s="2">
         <v>12</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="2">
         <v>1338</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="2">
         <v>8196</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="5">
+      <c r="B16" s="2">
         <v>13</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="2">
         <v>2695</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="2">
         <v>5821</v>
       </c>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="5">
+      <c r="B17" s="2">
         <v>14</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="2">
         <v>7830</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="2">
         <v>2087</v>
       </c>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="5">
+      <c r="B18" s="2">
         <v>15</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="2">
         <v>4154</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="2">
         <v>7243</v>
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="5">
+      <c r="B19" s="2">
         <v>16</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="2">
         <v>6381</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="2">
         <v>2394</v>
       </c>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="5">
+      <c r="B20" s="2">
         <v>17</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="2">
         <v>3387</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="2">
         <v>4907</v>
       </c>
     </row>
     <row r="21" spans="2:8">
-      <c r="B21" s="5">
+      <c r="B21" s="2">
         <v>18</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="2">
         <v>7395</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="2">
         <v>1309</v>
       </c>
     </row>
     <row r="22" spans="2:8">
-      <c r="B22" s="5">
+      <c r="B22" s="2">
         <v>19</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="2">
         <v>4368</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="2">
         <v>9166</v>
       </c>
     </row>
     <row r="23" spans="2:8">
-      <c r="B23" s="5">
+      <c r="B23" s="2">
         <v>20</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="2">
         <v>4232</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="2">
         <v>4023</v>
       </c>
     </row>
     <row r="24" spans="2:8">
-      <c r="B24" s="5">
+      <c r="B24" s="2">
         <v>21</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="2">
         <v>9058</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="2">
         <v>1338</v>
       </c>
     </row>
     <row r="25" spans="2:8">
-      <c r="B25" s="5">
+      <c r="B25" s="2">
         <v>22</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="2">
         <v>4905</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="2">
         <v>2695</v>
       </c>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="5">
+      <c r="B26" s="2">
         <v>23</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="2">
         <v>3712</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="2">
         <v>7830</v>
       </c>
     </row>
     <row r="27" spans="2:8">
-      <c r="B27" s="5">
+      <c r="B27" s="2">
         <v>24</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="2">
         <v>7555</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="2">
         <v>4154</v>
       </c>
     </row>
     <row r="28" spans="2:8">
-      <c r="B28" s="5">
+      <c r="B28" s="2">
         <v>25</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="2">
         <v>5309</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="2">
         <v>6381</v>
       </c>
     </row>
     <row r="29" spans="2:8">
-      <c r="B29" s="5">
+      <c r="B29" s="2">
         <v>26</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="2">
         <v>1682</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="2">
         <v>3387</v>
       </c>
     </row>
     <row r="30" spans="2:8">
-      <c r="B30" s="5">
+      <c r="B30" s="2">
         <v>27</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="2">
         <v>3885</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="2">
         <v>7395</v>
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="5">
+      <c r="B31" s="2">
         <v>28</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="2">
         <v>4589</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="2">
         <v>4368</v>
       </c>
     </row>
     <row r="32" spans="2:8">
-      <c r="B32" s="5">
+      <c r="B32" s="2">
         <v>29</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="2">
         <v>2109</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="2">
         <v>4232</v>
       </c>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="5">
+      <c r="B33" s="2">
         <v>30</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="2">
         <v>4006</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="2">
         <v>9058</v>
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="5">
+      <c r="B34" s="2">
         <v>31</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="C34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="2">
         <v>8164</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="2">
         <v>4905</v>
       </c>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="5">
+      <c r="B35" s="2">
         <v>32</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="2">
         <v>3084</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="2">
         <v>3712</v>
       </c>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="5">
+      <c r="B36" s="2">
         <v>33</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="C36" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="2">
         <v>8737</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="2">
         <v>7555</v>
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="5">
+      <c r="B37" s="2">
         <v>34</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="2">
         <v>8044</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="2">
         <v>5309</v>
       </c>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="5">
+      <c r="B38" s="2">
         <v>35</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="2">
         <v>8044</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="2">
         <v>1682</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="5">
+      <c r="B39" s="2">
         <v>36</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="C39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="2">
         <v>8044</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="2">
         <v>3885</v>
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="H40" s="5">
+      <c r="H40" s="2">
         <v>4589</v>
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="H41" s="5">
+      <c r="H41" s="2">
         <v>2109</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="H42" s="5">
+      <c r="H42" s="2">
         <v>4006</v>
       </c>
     </row>
     <row r="43" spans="2:8">
-      <c r="H43" s="5">
+      <c r="H43" s="2">
         <v>8164</v>
       </c>
     </row>
     <row r="44" spans="2:8">
-      <c r="H44" s="5">
+      <c r="H44" s="2">
         <v>3084</v>
       </c>
     </row>
     <row r="45" spans="2:8">
-      <c r="H45" s="5">
+      <c r="H45" s="2">
         <v>8737</v>
       </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="H46" s="5">
+      <c r="H46" s="2">
         <v>8044</v>
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="H47" s="5">
+      <c r="H47" s="2">
         <v>8044</v>
       </c>
     </row>
     <row r="48" spans="2:8">
-      <c r="H48" s="5">
+      <c r="H48" s="2">
         <v>8044</v>
       </c>
     </row>
@@ -4495,7 +4103,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Apr_15_ConditionalFunctional.20260415113706091.xlsx
+++ b/Apr_15_ConditionalFunctional.20260415113706091.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f009553a5688ab78/Documents/Desktop/Bytecode_training/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_CD756894645FB936B455ACD68D37F3B4289735EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8F3B225-BB7D-4D05-B508-CAD9152E4C25}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9000" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="If &amp; Ifs Notes" sheetId="4" r:id="rId1"/>
@@ -37,6 +31,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -44,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -389,8 +385,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,14 +425,151 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,30 +578,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79995117038483843"/>
+        <fgColor theme="7" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -781,14 +1106,262 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -796,18 +1369,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -843,53 +1434,69 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1147,240 +1754,243 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:P29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:P29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="88.88671875" customWidth="1"/>
-    <col min="4" max="4" width="48.5546875" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" customWidth="1"/>
+    <col min="3" max="3" width="88.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="48.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="38.5555555555556" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:16" ht="23.4">
-      <c r="C2" s="23" t="s">
+    <row r="1" ht="15.15"/>
+    <row r="2" ht="24.15" spans="3:16">
+      <c r="C2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="25"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="34"/>
     </row>
     <row r="4" spans="3:16">
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="47" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="3:16">
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="3:16">
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="36" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="3:16">
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="35" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="3:16">
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="35" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="3:16">
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="35" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="3:16">
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="3:16" ht="15.6">
-      <c r="C13" s="28" t="s">
+    <row r="13" ht="15.6" spans="3:16">
+      <c r="C13" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="3:16" ht="26.25" customHeight="1">
-      <c r="C14" s="29" t="s">
+    <row r="14" ht="26.25" customHeight="1" spans="3:16">
+      <c r="C14" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31" t="s">
+      <c r="F14" s="40"/>
+      <c r="G14" s="40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="3:16" ht="43.2">
-      <c r="C15" s="32" t="s">
+    <row r="15" ht="43.2" spans="3:16">
+      <c r="C15" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="42" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="3:16" ht="28.8">
-      <c r="C16" s="35" t="s">
+    <row r="16" ht="28.8" spans="3:16">
+      <c r="C16" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="36" t="s">
+      <c r="F16" s="5"/>
+      <c r="G16" s="45" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="3:4">
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="3:4">
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="3:4">
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B1:P37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="8" max="8" width="47.6640625" customWidth="1"/>
-    <col min="9" max="9" width="29.77734375" customWidth="1"/>
-    <col min="11" max="16" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="47.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="29.7777777777778" customWidth="1"/>
+    <col min="11" max="16" width="13.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16">
@@ -1399,720 +2009,720 @@
       <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="24" t="s">
         <v>50</v>
       </c>
       <c r="J1" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="2:16">
-      <c r="B2" s="2">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="5">
         <v>7899</v>
       </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="19" t="s">
+      <c r="H2" s="26"/>
+      <c r="I2" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="2" cm="1">
+      <c r="L2" s="5" cm="1">
         <f t="array" ref="L2">SUMIF(Cust_Name,K2,Sales)</f>
         <v>27881</v>
       </c>
-      <c r="M2" s="20" cm="1">
+      <c r="M2" s="28" cm="1">
         <f t="array" ref="M2">AVERAGEIF(Cust_Name,K2,Sales)</f>
-        <v>4646.8333333333303</v>
-      </c>
-      <c r="N2" s="2" cm="1">
+        <v>4646.83333333333</v>
+      </c>
+      <c r="N2" s="5" cm="1">
         <f t="array" ref="N2">COUNTIF(Cust_Name,K2)</f>
         <v>6</v>
       </c>
-      <c r="O2" s="2" cm="1">
+      <c r="O2" s="5" cm="1">
         <f t="array" ref="O2">_xlfn.MINIFS(Sales,Cust_Name,K2)</f>
         <v>1682</v>
       </c>
-      <c r="P2" s="2" cm="1">
+      <c r="P2" s="5" cm="1">
         <f t="array" ref="P2">_xlfn.MAXIFS(Sales,Cust_Name,K2)</f>
         <v>7830</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="2">
+      <c r="B3" s="5">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="5">
         <v>6146</v>
       </c>
-      <c r="H3" s="42"/>
-      <c r="I3" s="19" t="s">
+      <c r="H3" s="26"/>
+      <c r="I3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="2" cm="1">
+      <c r="L3" s="5" cm="1">
         <f t="array" ref="L3">SUMIF(Cust_Name,K3,Sales)</f>
         <v>23362</v>
       </c>
-      <c r="M3" s="20" cm="1">
+      <c r="M3" s="28" cm="1">
         <f t="array" ref="M3">AVERAGEIF(Cust_Name,K3,Sales)</f>
-        <v>3893.6666666666702</v>
-      </c>
-      <c r="N3" s="2" cm="1">
+        <v>3893.66666666667</v>
+      </c>
+      <c r="N3" s="5" cm="1">
         <f t="array" ref="N3">COUNTIF(Cust_Name,K3)</f>
         <v>6</v>
       </c>
-      <c r="O3" s="2" cm="1">
+      <c r="O3" s="5" cm="1">
         <f t="array" ref="O3">_xlfn.MINIFS(Sales,Cust_Name,K3)</f>
         <v>2087</v>
       </c>
-      <c r="P3" s="2" cm="1">
+      <c r="P3" s="5" cm="1">
         <f t="array" ref="P3">_xlfn.MAXIFS(Sales,Cust_Name,K3)</f>
         <v>8044</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="2">
+      <c r="B4" s="5">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="5">
         <v>8196</v>
       </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="19" t="s">
+      <c r="H4" s="26"/>
+      <c r="I4" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="2" cm="1">
+      <c r="L4" s="5" cm="1">
         <f t="array" ref="L4">SUMIF(Cust_Name,K4,Sales)</f>
         <v>38906</v>
       </c>
-      <c r="M4" s="20" cm="1">
+      <c r="M4" s="28" cm="1">
         <f t="array" ref="M4">AVERAGEIF(Cust_Name,K4,Sales)</f>
-        <v>6484.3333333333303</v>
-      </c>
-      <c r="N4" s="2" cm="1">
+        <v>6484.33333333333</v>
+      </c>
+      <c r="N4" s="5" cm="1">
         <f t="array" ref="N4">COUNTIF(Cust_Name,K4)</f>
         <v>6</v>
       </c>
-      <c r="O4" s="2" cm="1">
+      <c r="O4" s="5" cm="1">
         <f t="array" ref="O4">_xlfn.MINIFS(Sales,Cust_Name,K4)</f>
         <v>4589</v>
       </c>
-      <c r="P4" s="2" cm="1">
+      <c r="P4" s="5" cm="1">
         <f t="array" ref="P4">_xlfn.MAXIFS(Sales,Cust_Name,K4)</f>
         <v>9166</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
-      <c r="B5" s="2">
+    <row r="5" ht="15.15" spans="2:16">
+      <c r="B5" s="5">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="5">
         <v>5821</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="21" t="s">
+      <c r="H5" s="29"/>
+      <c r="I5" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="2" cm="1">
+      <c r="K5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="5" cm="1">
         <f t="array" ref="L5">SUMIF(Cust_Name,K5,Sales)</f>
         <v>101749</v>
       </c>
-      <c r="M5" s="20" cm="1">
+      <c r="M5" s="28" cm="1">
         <f t="array" ref="M5">AVERAGEIF(Cust_Name,K5,Sales)</f>
-        <v>5652.7222222222199</v>
-      </c>
-      <c r="N5" s="2" cm="1">
+        <v>5652.72222222222</v>
+      </c>
+      <c r="N5" s="5" cm="1">
         <f t="array" ref="N5">COUNTIF(Cust_Name,K5)</f>
         <v>18</v>
       </c>
-      <c r="O5" s="2" cm="1">
+      <c r="O5" s="5" cm="1">
         <f t="array" ref="O5">_xlfn.MINIFS(Sales,Cust_Name,K5)</f>
         <v>1309</v>
       </c>
-      <c r="P5" s="2" cm="1">
+      <c r="P5" s="5" cm="1">
         <f t="array" ref="P5">_xlfn.MAXIFS(Sales,Cust_Name,K5)</f>
         <v>9058</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="2">
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="5">
         <v>2087</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="2">
+      <c r="B7" s="5">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="5">
         <v>7243</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="5">
         <f>SUMIF(C:C,"Ravi",F:F)</f>
         <v>101749</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="O7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="P7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="2">
+      <c r="B8" s="5">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="5">
         <v>2394</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="5">
         <f>COUNTIF(C:C,"Ravi")</f>
         <v>18</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="2" cm="1">
+      <c r="L8" s="5" cm="1">
         <f t="array" ref="L8">SUMIF(Region,K8,Sales)</f>
         <v>43947</v>
       </c>
-      <c r="M8" s="20" cm="1">
+      <c r="M8" s="28" cm="1">
         <f t="array" ref="M8">AVERAGEIF(Region,K8,Sales)</f>
         <v>4883</v>
       </c>
-      <c r="N8" s="2" cm="1">
+      <c r="N8" s="5" cm="1">
         <f t="array" ref="N8">COUNTIF(Region,K8)</f>
         <v>9</v>
       </c>
-      <c r="O8" s="2" cm="1">
+      <c r="O8" s="5" cm="1">
         <f t="array" ref="O8">_xlfn.MINIFS(Sales,Region,K8)</f>
         <v>1309</v>
       </c>
-      <c r="P8" s="2"/>
+      <c r="P8" s="5"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="2">
+      <c r="B9" s="5">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="5">
         <v>4907</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="5">
         <f>AVERAGEIF(D:D,"South",F:F)</f>
         <v>6037.4</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="2" cm="1">
+      <c r="L9" s="5" cm="1">
         <f t="array" ref="L9">SUMIF(Region,K9,Sales)</f>
         <v>56198</v>
       </c>
-      <c r="M9" s="20" cm="1">
+      <c r="M9" s="28" cm="1">
         <f t="array" ref="M9">AVERAGEIF(Region,K9,Sales)</f>
-        <v>5108.9090909090901</v>
-      </c>
-      <c r="N9" s="2" cm="1">
+        <v>5108.90909090909</v>
+      </c>
+      <c r="N9" s="5" cm="1">
         <f t="array" ref="N9">COUNTIF(Region,K9)</f>
         <v>11</v>
       </c>
-      <c r="O9" s="2" cm="1">
+      <c r="O9" s="5" cm="1">
         <f t="array" ref="O9">_xlfn.MINIFS(Sales,Region,K9)</f>
         <v>2087</v>
       </c>
-      <c r="P9" s="2"/>
+      <c r="P9" s="5"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>9</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="5">
         <v>1309</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="5">
         <f>_xlfn.MAXIFS(F:F,E:E,"Electronics")</f>
         <v>9058</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="L10" s="2" cm="1">
+      <c r="L10" s="5" cm="1">
         <f t="array" ref="L10">SUMIF(Region,K10,Sales)</f>
         <v>61566</v>
       </c>
-      <c r="M10" s="20" cm="1">
+      <c r="M10" s="28" cm="1">
         <f t="array" ref="M10">AVERAGEIF(Region,K10,Sales)</f>
-        <v>5596.9090909090901</v>
-      </c>
-      <c r="N10" s="2" cm="1">
+        <v>5596.90909090909</v>
+      </c>
+      <c r="N10" s="5" cm="1">
         <f t="array" ref="N10">COUNTIF(Region,K10)</f>
         <v>11</v>
       </c>
-      <c r="O10" s="2" cm="1">
+      <c r="O10" s="5" cm="1">
         <f t="array" ref="O10">_xlfn.MINIFS(Sales,Region,K10)</f>
         <v>1682</v>
       </c>
-      <c r="P10" s="2"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="2">
+      <c r="B11" s="5">
         <v>10</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="5">
         <v>9166</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="5">
         <f>_xlfn.MINIFS(F:F,E:E,"Fashion")</f>
         <v>1338</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="2" cm="1">
+      <c r="L11" s="5" cm="1">
         <f t="array" ref="L11">SUMIF(Region,K11,Sales)</f>
         <v>30187</v>
       </c>
-      <c r="M11" s="20" cm="1">
+      <c r="M11" s="28" cm="1">
         <f t="array" ref="M11">AVERAGEIF(Region,K11,Sales)</f>
         <v>6037.4</v>
       </c>
-      <c r="N11" s="2" cm="1">
+      <c r="N11" s="5" cm="1">
         <f t="array" ref="N11">COUNTIF(Region,K11)</f>
         <v>5</v>
       </c>
-      <c r="O11" s="2" cm="1">
+      <c r="O11" s="5" cm="1">
         <f t="array" ref="O11">_xlfn.MINIFS(Sales,Region,K11)</f>
         <v>2695</v>
       </c>
-      <c r="P11" s="2"/>
+      <c r="P11" s="5"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="2">
+      <c r="B12" s="5">
         <v>11</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="5">
         <v>4023</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="2">
+      <c r="B13" s="5">
         <v>12</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="5">
         <v>1338</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="K13" s="18" t="s">
+      <c r="I13" s="31"/>
+      <c r="K13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="M13" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="O13" s="18" t="s">
+      <c r="O13" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="P13" s="18" t="s">
+      <c r="P13" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="2">
+      <c r="B14" s="5">
         <v>13</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="5">
         <v>2695</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="31">
         <f>SUMIFS(F:F,D:D,"South")</f>
         <v>30187</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <v>14</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="5">
         <v>7830</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="31">
         <f>COUNTIFS(E:E,"Electronics",D:D,"South")</f>
         <v>4</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="5">
         <v>4154</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="31">
         <f>AVERAGEIFS(F:F,E:E,"Fashion",D:D,"North")</f>
         <v>5353.875</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="2">
+      <c r="B17" s="5">
         <v>16</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="5">
         <v>6381</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="31">
         <f>COUNTIFS(F:F,"&gt;5000")</f>
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="2">
+      <c r="B18" s="5">
         <v>17</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="5">
         <v>3387</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="2">
+      <c r="B19" s="5">
         <v>18</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="5">
         <v>7395</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="2">
+      <c r="B20" s="5">
         <v>19</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="5">
         <v>4368</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="2">
+      <c r="B21" s="5">
         <v>20</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="5">
         <v>4232</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="2">
+      <c r="B22" s="5">
         <v>21</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="5">
         <v>9058</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="2">
+      <c r="B23" s="5">
         <v>22</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="5">
         <v>4905</v>
       </c>
       <c r="H23" t="s">
@@ -2120,240 +2730,240 @@
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="2">
+      <c r="B24" s="5">
         <v>23</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="5">
         <v>3712</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="2">
+      <c r="B25" s="5">
         <v>24</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="C25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="5">
         <v>7555</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="2">
+      <c r="B26" s="5">
         <v>25</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="5">
         <v>5309</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="2">
+      <c r="B27" s="5">
         <v>26</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="5">
         <v>1682</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="2">
+      <c r="B28" s="5">
         <v>27</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="5">
         <v>3885</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="2">
+      <c r="B29" s="5">
         <v>28</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="5">
         <v>4589</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="2">
+      <c r="B30" s="5">
         <v>29</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="5">
         <v>2109</v>
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="2">
+      <c r="B31" s="5">
         <v>30</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="C31" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="5">
         <v>4006</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="2">
+      <c r="B32" s="5">
         <v>31</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="C32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="5">
         <v>8164</v>
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="2">
+      <c r="B33" s="5">
         <v>32</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="5">
         <v>3084</v>
       </c>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="2">
+      <c r="B34" s="5">
         <v>33</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="5">
         <v>8737</v>
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="2">
+      <c r="B35" s="5">
         <v>34</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="5">
         <v>8044</v>
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="2">
+      <c r="B36" s="5">
         <v>35</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="5">
         <v>8044</v>
       </c>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="2">
+      <c r="B37" s="5">
         <v>36</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="C37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="5">
         <v>8044</v>
       </c>
     </row>
@@ -2362,16 +2972,18 @@
     <mergeCell ref="H1:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75783AB-BA76-468B-9550-A67D45F2A8EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="D2:D38"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:4">
@@ -2380,196 +2992,198 @@
       </c>
     </row>
     <row r="3" spans="4:4">
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="4:4">
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="4:4">
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="4:4">
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="4:4">
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="4:4">
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="4:4">
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="4:4">
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="4:4">
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="4:4">
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="14" spans="4:4">
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" spans="4:4">
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="4:4">
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="17" spans="4:4">
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="4:4">
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="19" spans="4:4">
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="20" spans="4:4">
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="21" spans="4:4">
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="4:4">
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="4:4">
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="25" spans="4:4">
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" spans="4:4">
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="27" spans="4:4">
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="28" spans="4:4">
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="4:4">
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="4:4">
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="4:4">
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" spans="4:4">
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="33" spans="4:4">
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" spans="4:4">
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="4:4">
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="36" spans="4:4">
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="37" spans="4:4">
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="38" spans="4:4">
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="5" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="E2:O28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="15" max="15" width="9.6640625"/>
+    <col min="15" max="15" width="9.66666666666667"/>
   </cols>
   <sheetData>
     <row r="2" spans="5:15">
@@ -2745,34 +3359,34 @@
       </c>
     </row>
     <row r="18" spans="5:15">
-      <c r="F18" s="16">
+      <c r="F18" s="22">
         <v>1</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="22">
         <v>2</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="22">
         <v>3</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="22">
         <v>4</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="22">
         <v>5</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="22">
         <v>6</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="22">
         <v>7</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="22">
         <v>8</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="22">
         <v>9</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="22">
         <v>10</v>
       </c>
     </row>
@@ -3228,23 +3842,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B3:L48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:L48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="17.2222222222222" customWidth="1"/>
+    <col min="10" max="10" width="19.3333333333333" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="19.21875" customWidth="1"/>
+    <col min="12" max="12" width="19.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12">
+    <row r="2" ht="15.15"/>
+    <row r="3" ht="15.15" spans="2:12">
       <c r="B3" s="1" t="s">
         <v>44</v>
       </c>
@@ -3260,240 +3877,240 @@
       <c r="F3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="46"/>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="2">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" ht="15.15" spans="2:12">
+      <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="5">
         <v>7899</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="2">
+    <row r="5" ht="15.15" spans="2:12">
+      <c r="B5" s="5">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="5">
         <v>6146</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="9">
         <f>SUM(sum)</f>
         <v>191898</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="10">
         <f>AVERAGE(sum)</f>
         <v>5330.5</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="10">
         <f>MIN(sum)</f>
         <v>1309</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="10">
         <f>MAX(sum)</f>
         <v>9166</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="11">
         <f>COUNT(sum)</f>
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="2">
+    <row r="6" ht="15.15" spans="2:12">
+      <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="5">
         <v>8196</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="2">
+    <row r="7" ht="15.15" spans="2:12">
+      <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="5">
         <v>5821</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="49"/>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="2">
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" ht="15.15" spans="2:12">
+      <c r="B8" s="5">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="5">
         <v>2087</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="2">
+    <row r="9" ht="15.15" spans="2:12">
+      <c r="B9" s="5">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="5">
         <v>7243</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="18">
         <v>200000</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="19">
         <f>$H$5</f>
         <v>191898</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="20">
         <f>$H$5/$H$9</f>
-        <v>0.95948999999999995</v>
-      </c>
-      <c r="K9" s="13">
+        <v>0.95949</v>
+      </c>
+      <c r="K9" s="19">
         <f>$H$9-$H$5</f>
         <v>8102</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="21">
         <f>($H$9-$H$5)/$H$9</f>
-        <v>4.0509999999999997E-2</v>
+        <v>0.04051</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>7</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="5">
         <v>2394</v>
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="2">
+      <c r="B11" s="5">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="5">
         <v>4907</v>
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="2">
+      <c r="B12" s="5">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="5">
         <v>1309</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -3501,587 +4118,587 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="2">
+      <c r="B13" s="5">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="5">
         <v>9166</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="5">
         <v>7899</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="2">
+      <c r="B14" s="5">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="5">
         <v>4023</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="5">
         <v>6146</v>
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="5">
         <v>1338</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="5">
         <v>8196</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>13</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="5">
         <v>2695</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="5">
         <v>5821</v>
       </c>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="2">
+      <c r="B17" s="5">
         <v>14</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="5">
         <v>7830</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="5">
         <v>2087</v>
       </c>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="2">
+      <c r="B18" s="5">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="C18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="5">
         <v>4154</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="5">
         <v>7243</v>
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="2">
+      <c r="B19" s="5">
         <v>16</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="5">
         <v>6381</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="5">
         <v>2394</v>
       </c>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="2">
+      <c r="B20" s="5">
         <v>17</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="5">
         <v>3387</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="5">
         <v>4907</v>
       </c>
     </row>
     <row r="21" spans="2:8">
-      <c r="B21" s="2">
+      <c r="B21" s="5">
         <v>18</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="C21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="5">
         <v>7395</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="5">
         <v>1309</v>
       </c>
     </row>
     <row r="22" spans="2:8">
-      <c r="B22" s="2">
+      <c r="B22" s="5">
         <v>19</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="5">
         <v>4368</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="5">
         <v>9166</v>
       </c>
     </row>
     <row r="23" spans="2:8">
-      <c r="B23" s="2">
+      <c r="B23" s="5">
         <v>20</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="5">
         <v>4232</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="5">
         <v>4023</v>
       </c>
     </row>
     <row r="24" spans="2:8">
-      <c r="B24" s="2">
+      <c r="B24" s="5">
         <v>21</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="5">
         <v>9058</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="5">
         <v>1338</v>
       </c>
     </row>
     <row r="25" spans="2:8">
-      <c r="B25" s="2">
+      <c r="B25" s="5">
         <v>22</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="5">
         <v>4905</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="5">
         <v>2695</v>
       </c>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="2">
+      <c r="B26" s="5">
         <v>23</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="5">
         <v>3712</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="5">
         <v>7830</v>
       </c>
     </row>
     <row r="27" spans="2:8">
-      <c r="B27" s="2">
+      <c r="B27" s="5">
         <v>24</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="5">
         <v>7555</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="5">
         <v>4154</v>
       </c>
     </row>
     <row r="28" spans="2:8">
-      <c r="B28" s="2">
+      <c r="B28" s="5">
         <v>25</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="5">
         <v>5309</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="5">
         <v>6381</v>
       </c>
     </row>
     <row r="29" spans="2:8">
-      <c r="B29" s="2">
+      <c r="B29" s="5">
         <v>26</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="5">
         <v>1682</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="5">
         <v>3387</v>
       </c>
     </row>
     <row r="30" spans="2:8">
-      <c r="B30" s="2">
+      <c r="B30" s="5">
         <v>27</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="C30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="5">
         <v>3885</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="5">
         <v>7395</v>
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="2">
+      <c r="B31" s="5">
         <v>28</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="5">
         <v>4589</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="5">
         <v>4368</v>
       </c>
     </row>
     <row r="32" spans="2:8">
-      <c r="B32" s="2">
+      <c r="B32" s="5">
         <v>29</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="5">
         <v>2109</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="5">
         <v>4232</v>
       </c>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="2">
+      <c r="B33" s="5">
         <v>30</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="C33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="5">
         <v>4006</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="5">
         <v>9058</v>
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="2">
+      <c r="B34" s="5">
         <v>31</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="5">
         <v>8164</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="5">
         <v>4905</v>
       </c>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="2">
+      <c r="B35" s="5">
         <v>32</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="5">
         <v>3084</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="5">
         <v>3712</v>
       </c>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="2">
+      <c r="B36" s="5">
         <v>33</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="C36" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="5">
         <v>8737</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="5">
         <v>7555</v>
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="2">
+      <c r="B37" s="5">
         <v>34</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="5">
         <v>8044</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="5">
         <v>5309</v>
       </c>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="2">
+      <c r="B38" s="5">
         <v>35</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="5">
         <v>8044</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="5">
         <v>1682</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="2">
+      <c r="B39" s="5">
         <v>36</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="C39" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="5">
         <v>8044</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="5">
         <v>3885</v>
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="H40" s="2">
+      <c r="H40" s="5">
         <v>4589</v>
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="H41" s="2">
+      <c r="H41" s="5">
         <v>2109</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="H42" s="2">
+      <c r="H42" s="5">
         <v>4006</v>
       </c>
     </row>
     <row r="43" spans="2:8">
-      <c r="H43" s="2">
+      <c r="H43" s="5">
         <v>8164</v>
       </c>
     </row>
     <row r="44" spans="2:8">
-      <c r="H44" s="2">
+      <c r="H44" s="5">
         <v>3084</v>
       </c>
     </row>
     <row r="45" spans="2:8">
-      <c r="H45" s="2">
+      <c r="H45" s="5">
         <v>8737</v>
       </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="H46" s="2">
+      <c r="H46" s="5">
         <v>8044</v>
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="H47" s="2">
+      <c r="H47" s="5">
         <v>8044</v>
       </c>
     </row>
     <row r="48" spans="2:8">
-      <c r="H48" s="2">
+      <c r="H48" s="5">
         <v>8044</v>
       </c>
     </row>
@@ -4103,6 +4720,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>